--- a/Negocios/Actividad 3 Negocio/Diagrama de grantt.xlsx
+++ b/Negocios/Actividad 3 Negocio/Diagrama de grantt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\Analisis y desarrollo de software\Instructor Cesar Chacon\Segundo Trimestre\Negocios\Actividad 3 Negocio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE28BC3-1573-49F8-8C79-E535C772C82C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F10D65AE-90FD-42C1-B9DA-F3AE97750405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="38">
   <si>
     <t>Levantamiento de requisitos</t>
   </si>
@@ -99,10 +99,55 @@
     <t>FIN</t>
   </si>
   <si>
-    <t xml:space="preserve">PERONA X </t>
+    <t>INICIO DEL PROYECTO</t>
   </si>
   <si>
-    <t>INICIO DEL PROYECTO</t>
+    <t xml:space="preserve">Mes 1 </t>
+  </si>
+  <si>
+    <t>mes 2</t>
+  </si>
+  <si>
+    <t>mes 3</t>
+  </si>
+  <si>
+    <t>mes 4</t>
+  </si>
+  <si>
+    <t>mes5</t>
+  </si>
+  <si>
+    <t>mes 6</t>
+  </si>
+  <si>
+    <t>Equipo desarrollo</t>
+  </si>
+  <si>
+    <t>Power Owner</t>
+  </si>
+  <si>
+    <t>Backend Developer</t>
+  </si>
+  <si>
+    <t>Scrum Master/Arquitecto</t>
+  </si>
+  <si>
+    <t>Frontend Developer</t>
+  </si>
+  <si>
+    <t>IA Developer</t>
+  </si>
+  <si>
+    <t>Backend / Frontend Developer</t>
+  </si>
+  <si>
+    <t>QA Tester</t>
+  </si>
+  <si>
+    <t>Scrum Master</t>
+  </si>
+  <si>
+    <t>Product Owner</t>
   </si>
 </sst>
 </file>
@@ -110,9 +155,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="172" formatCode="dd/mm/yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -165,8 +210,45 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -191,8 +273,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -200,52 +312,96 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="172" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -262,6 +418,2930 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-CO"/>
+              <a:t>tarea</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="es-CO" sz="1600" b="1" i="0" u="none" strike="noStrike" cap="all" normalizeH="0" baseline="0"/>
+              <a:t>Cronograma del Proyecto Senalingua</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="es-CO"/>
+              <a:t>s</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="es-CO" baseline="0"/>
+              <a:t> </a:t>
+            </a:r>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-CO"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Mes 1</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$A$26:$A$41</c:f>
+              <c:strCache>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>Levantamiento de requisitos</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Diseño base de datos</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Diseño arquitectura</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Desarrollo Backend</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Autenticación y Roles</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>CRUD Lecciones</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Desarrollo Frontend</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Sistema de Gamificación</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Integración IA</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Evaluaciones</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Seguimiento del progreso</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Pruebas funcionales</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Pruebas con usuarios</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Ajustes finales</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Documentación</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Entrega final</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$B$26:$B$41</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FD60-465C-BAE9-2FD841E216B1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Mes 2</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$A$26:$A$41</c:f>
+              <c:strCache>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>Levantamiento de requisitos</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Diseño base de datos</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Diseño arquitectura</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Desarrollo Backend</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Autenticación y Roles</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>CRUD Lecciones</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Desarrollo Frontend</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Sistema de Gamificación</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Integración IA</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Evaluaciones</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Seguimiento del progreso</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Pruebas funcionales</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Pruebas con usuarios</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Ajustes finales</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Documentación</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Entrega final</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$C$26:$C$41</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-FD60-465C-BAE9-2FD841E216B1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Mes 3</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$A$26:$A$41</c:f>
+              <c:strCache>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>Levantamiento de requisitos</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Diseño base de datos</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Diseño arquitectura</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Desarrollo Backend</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Autenticación y Roles</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>CRUD Lecciones</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Desarrollo Frontend</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Sistema de Gamificación</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Integración IA</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Evaluaciones</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Seguimiento del progreso</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Pruebas funcionales</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Pruebas con usuarios</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Ajustes finales</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Documentación</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Entrega final</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$D$26:$D$41</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-FD60-465C-BAE9-2FD841E216B1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>Mes 4</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$A$26:$A$41</c:f>
+              <c:strCache>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>Levantamiento de requisitos</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Diseño base de datos</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Diseño arquitectura</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Desarrollo Backend</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Autenticación y Roles</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>CRUD Lecciones</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Desarrollo Frontend</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Sistema de Gamificación</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Integración IA</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Evaluaciones</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Seguimiento del progreso</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Pruebas funcionales</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Pruebas con usuarios</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Ajustes finales</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Documentación</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Entrega final</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$E$26:$E$41</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="6">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-FD60-465C-BAE9-2FD841E216B1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>Mes 5</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$A$26:$A$41</c:f>
+              <c:strCache>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>Levantamiento de requisitos</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Diseño base de datos</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Diseño arquitectura</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Desarrollo Backend</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Autenticación y Roles</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>CRUD Lecciones</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Desarrollo Frontend</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Sistema de Gamificación</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Integración IA</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Evaluaciones</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Seguimiento del progreso</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Pruebas funcionales</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Pruebas con usuarios</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Ajustes finales</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Documentación</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Entrega final</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$F$26:$F$41</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="8">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-FD60-465C-BAE9-2FD841E216B1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:v>Mes 6</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$A$26:$A$41</c:f>
+              <c:strCache>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>Levantamiento de requisitos</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Diseño base de datos</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Diseño arquitectura</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Desarrollo Backend</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Autenticación y Roles</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>CRUD Lecciones</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Desarrollo Frontend</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Sistema de Gamificación</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Integración IA</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Evaluaciones</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Seguimiento del progreso</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Pruebas funcionales</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Pruebas con usuarios</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Ajustes finales</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Documentación</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Entrega final</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$G$26:$G$41</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="14">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-FD60-465C-BAE9-2FD841E216B1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="79"/>
+        <c:overlap val="100"/>
+        <c:axId val="92902512"/>
+        <c:axId val="92902992"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="92902512"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="92902992"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="92902992"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="92902512"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-CO"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-CO"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-CO" b="1"/>
+              <a:t>Progreso</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-CO"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="7"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="8"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="9"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="10"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="11"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="12"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="13"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="14"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="15"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$B$7:$B$22</c:f>
+              <c:strCache>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>Power Owner</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Backend Developer</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Scrum Master/Arquitecto</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Backend Developer</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Backend Developer</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Backend Developer</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Frontend Developer</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Frontend Developer</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>IA Developer</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Backend / Frontend Developer</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Backend Developer</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>QA Tester</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>QA Tester</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Equipo desarrollo</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Scrum Master</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Product Owner</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$C$7:$C$22</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-91DC-46BE-87F6-3C85048B9FB0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="75"/>
+      </c:doughnutChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-CO"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-CO"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="298">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="800" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="800" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>594360</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>289560</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBBBD815-A01A-4057-147E-DB96F33849F8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>472440</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>289560</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{765B1D4F-756C-276D-4A38-31D8D1B42251}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -527,378 +3607,628 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="30.77734375" customWidth="1"/>
-    <col min="3" max="5" width="11.77734375" customWidth="1"/>
+    <col min="1" max="1" width="30.77734375" customWidth="1"/>
+    <col min="2" max="2" width="25.77734375" customWidth="1"/>
+    <col min="3" max="7" width="25.77734375" style="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
     </row>
     <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
+      <c r="A3" s="3"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
     </row>
     <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="4"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
+      <c r="A4" s="3"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="4"/>
-      <c r="B5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="9">
+      <c r="A5" s="3"/>
+      <c r="B5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" s="7">
         <v>46084</v>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
     </row>
     <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="13">
+      <c r="B7" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="11">
         <v>1</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="12">
         <v>46084</v>
       </c>
-      <c r="E7" s="14">
-        <v>46268</v>
-      </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
+      <c r="E7" s="12">
+        <v>46096</v>
+      </c>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="13">
+      <c r="B8" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="11">
         <v>1</v>
       </c>
-      <c r="D8" s="14">
-        <v>46085</v>
-      </c>
-      <c r="E8" s="14">
-        <v>46269</v>
-      </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
+      <c r="D8" s="12">
+        <v>46097</v>
+      </c>
+      <c r="E8" s="12">
+        <v>46111</v>
+      </c>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="13">
+      <c r="B9" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="11">
         <v>1</v>
       </c>
-      <c r="D9" s="14">
-        <v>46086</v>
-      </c>
-      <c r="E9" s="14">
-        <v>46270</v>
-      </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
+      <c r="D9" s="12">
+        <v>46112</v>
+      </c>
+      <c r="E9" s="12">
+        <v>46122</v>
+      </c>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="13">
-        <v>1</v>
-      </c>
-      <c r="D10" s="14">
-        <v>46087</v>
-      </c>
-      <c r="E10" s="14">
-        <v>46271</v>
-      </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
+      <c r="B10" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="11">
+        <v>0.6</v>
+      </c>
+      <c r="D10" s="12">
+        <v>46123</v>
+      </c>
+      <c r="E10" s="12">
+        <v>46173</v>
+      </c>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="13">
-        <v>1</v>
-      </c>
-      <c r="D11" s="14">
-        <v>46088</v>
-      </c>
-      <c r="E11" s="14">
-        <v>46272</v>
-      </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
+      <c r="B11" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D11" s="12">
+        <v>46143</v>
+      </c>
+      <c r="E11" s="12">
+        <v>46162</v>
+      </c>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
     </row>
     <row r="12" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="13">
-        <v>1</v>
-      </c>
-      <c r="D12" s="14">
-        <v>46089</v>
-      </c>
-      <c r="E12" s="14">
-        <v>46273</v>
-      </c>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
+      <c r="B12" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D12" s="12">
+        <v>46163</v>
+      </c>
+      <c r="E12" s="12">
+        <v>46183</v>
+      </c>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
     </row>
     <row r="13" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="13">
-        <v>1</v>
-      </c>
-      <c r="D13" s="14">
-        <v>46090</v>
-      </c>
-      <c r="E13" s="14">
-        <v>46274</v>
-      </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
+      <c r="B13" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="D13" s="12">
+        <v>46184</v>
+      </c>
+      <c r="E13" s="12">
+        <v>46213</v>
+      </c>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
     </row>
     <row r="14" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="13">
-        <v>1</v>
-      </c>
-      <c r="D14" s="14">
-        <v>46091</v>
-      </c>
-      <c r="E14" s="14">
-        <v>46275</v>
-      </c>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
+      <c r="B14" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="D14" s="12">
+        <v>46214</v>
+      </c>
+      <c r="E14" s="12">
+        <v>46228</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
     </row>
     <row r="15" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="13">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14">
-        <v>46092</v>
-      </c>
-      <c r="E15" s="14">
-        <v>46276</v>
-      </c>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
+      <c r="B15" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="D15" s="12">
+        <v>46229</v>
+      </c>
+      <c r="E15" s="12">
+        <v>46244</v>
+      </c>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
     </row>
     <row r="16" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="13">
-        <v>1</v>
-      </c>
-      <c r="D16" s="14">
-        <v>46093</v>
-      </c>
-      <c r="E16" s="14">
-        <v>46277</v>
-      </c>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
+      <c r="B16" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="D16" s="12">
+        <v>46245</v>
+      </c>
+      <c r="E16" s="12">
+        <v>46254</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
     </row>
     <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="13">
-        <v>1</v>
-      </c>
-      <c r="D17" s="14">
-        <v>46094</v>
-      </c>
-      <c r="E17" s="14">
-        <v>46278</v>
-      </c>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
+      <c r="B17" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="D17" s="12">
+        <v>46255</v>
+      </c>
+      <c r="E17" s="12">
+        <v>46262</v>
+      </c>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
     </row>
     <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="13">
-        <v>1</v>
-      </c>
-      <c r="D18" s="14">
-        <v>46095</v>
-      </c>
-      <c r="E18" s="14">
-        <v>46279</v>
-      </c>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
+      <c r="B18" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="D18" s="12">
+        <v>46263</v>
+      </c>
+      <c r="E18" s="12">
+        <v>46270</v>
+      </c>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
     </row>
     <row r="19" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="13">
-        <v>1</v>
-      </c>
-      <c r="D19" s="14">
-        <v>46096</v>
-      </c>
-      <c r="E19" s="14">
+      <c r="B19" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="11">
+        <v>0.1</v>
+      </c>
+      <c r="D19" s="12">
+        <v>46271</v>
+      </c>
+      <c r="E19" s="12">
         <v>46280</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="13">
-        <v>1</v>
-      </c>
-      <c r="D20" s="14">
-        <v>46097</v>
-      </c>
-      <c r="E20" s="14">
+      <c r="B20" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="11">
+        <v>0</v>
+      </c>
+      <c r="D20" s="12">
         <v>46281</v>
+      </c>
+      <c r="E20" s="12">
+        <v>46290</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="13">
-        <v>1</v>
-      </c>
-      <c r="D21" s="14">
-        <v>46098</v>
-      </c>
-      <c r="E21" s="14">
-        <v>46282</v>
+      <c r="B21" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="11">
+        <v>0</v>
+      </c>
+      <c r="D21" s="12">
+        <v>46291</v>
+      </c>
+      <c r="E21" s="12">
+        <v>46295</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" s="13">
+      <c r="B22" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="11">
+        <v>0</v>
+      </c>
+      <c r="D22" s="12">
+        <v>46296</v>
+      </c>
+      <c r="E22" s="12">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="15"/>
+      <c r="B24" s="14"/>
+    </row>
+    <row r="25" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A25" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A26" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="21">
         <v>1</v>
       </c>
-      <c r="D22" s="14">
-        <v>46099</v>
-      </c>
-      <c r="E22" s="14">
-        <v>46283</v>
-      </c>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+    </row>
+    <row r="27" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A27" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B27" s="21">
+        <v>1</v>
+      </c>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+    </row>
+    <row r="28" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A28" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" s="21">
+        <v>1</v>
+      </c>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+    </row>
+    <row r="29" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A29" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" s="22"/>
+      <c r="C29" s="25">
+        <v>2</v>
+      </c>
+      <c r="D29" s="26">
+        <v>3</v>
+      </c>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+    </row>
+    <row r="30" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A30" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="22"/>
+      <c r="C30" s="25">
+        <v>2</v>
+      </c>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+    </row>
+    <row r="31" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A31" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31" s="22"/>
+      <c r="C31" s="25">
+        <v>2</v>
+      </c>
+      <c r="D31" s="26">
+        <v>3</v>
+      </c>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+    </row>
+    <row r="32" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A32" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="26">
+        <v>3</v>
+      </c>
+      <c r="E32" s="18">
+        <v>4</v>
+      </c>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+    </row>
+    <row r="33" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A33" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="18">
+        <v>4</v>
+      </c>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+    </row>
+    <row r="34" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A34" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="18">
+        <v>4</v>
+      </c>
+      <c r="F34" s="27">
+        <v>5</v>
+      </c>
+      <c r="G34" s="22"/>
+    </row>
+    <row r="35" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A35" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="22"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="18">
+        <v>4</v>
+      </c>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+    </row>
+    <row r="36" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A36" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="18">
+        <v>4</v>
+      </c>
+      <c r="F36" s="27">
+        <v>5</v>
+      </c>
+      <c r="G36" s="22"/>
+    </row>
+    <row r="37" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A37" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="27">
+        <v>5</v>
+      </c>
+      <c r="G37" s="22"/>
+    </row>
+    <row r="38" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A38" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" s="22"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="27">
+        <v>5</v>
+      </c>
+      <c r="G38" s="22"/>
+    </row>
+    <row r="39" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A39" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" s="22"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="27">
+        <v>5</v>
+      </c>
+      <c r="G39" s="22"/>
+    </row>
+    <row r="40" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A40" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B40" s="22"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A41" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" s="24"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>